--- a/templates_word/FORMATO_PLANTILLA.xlsx
+++ b/templates_word/FORMATO_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SistemaBeneficiarios\templates_word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DA93F2-B903-4124-8404-8C73B9856DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818F8A11-7B64-4C07-ADDD-E1C302DF28A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>PLANILLA DE ASISTENCIA DE TRABAJO COMUNITARIO</t>
   </si>
@@ -44,12 +44,6 @@
   </si>
   <si>
     <t>HORAS DE TRABAJO</t>
-  </si>
-  <si>
-    <t>UNIDAD EDUCATIVA</t>
-  </si>
-  <si>
-    <t>DISTRITO</t>
   </si>
   <si>
     <t>ACTIVIDAD REALIZADA</t>
@@ -162,15 +156,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>296885</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>430235</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>39192</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -192,8 +186,58 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="400050" y="342900"/>
-          <a:ext cx="687410" cy="800100"/>
+          <a:off x="123825" y="323849"/>
+          <a:ext cx="868385" cy="1010743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>370301</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F6CFD5D-5E0F-42EF-A39D-A254532EBD95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8924925" y="361950"/>
+          <a:ext cx="2037176" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -505,15 +549,16 @@
   <dimension ref="A4:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" customWidth="1"/>
-    <col min="9" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -560,42 +605,35 @@
       <c r="J6" s="3"/>
     </row>
     <row r="9" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="10" spans="1:11" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -605,7 +643,6 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
